--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE5D787-0CB6-405D-9FB6-2CF25E0A27BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903684CC-0FCE-4B9F-8CE2-F1AA2D644A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>שלא יהיה כפתור delete על הגרסה בעמוד של הקורס</t>
+  </si>
+  <si>
+    <t>ניסיתי להוסיף קורס בנושא חדש ואז הופיעה לי ההודעה subject must be one of the following values:</t>
+  </si>
+  <si>
+    <t>אני רוצה שלחיצה על הקורס בin progress תוביל ישר לדף של הגרסה שרשומים אליה</t>
   </si>
 </sst>
 </file>
@@ -630,12 +636,18 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903684CC-0FCE-4B9F-8CE2-F1AA2D644A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BDD47F-4CF5-4BE4-8980-CE1AD5F688C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>אני רוצה שלחיצה על הקורס בin progress תוביל ישר לדף של הגרסה שרשומים אליה</t>
+  </si>
+  <si>
+    <t>שלחיצה על other בסינון קורסים מתחת לחיפוש יפתח רשימה של כל האופציות האחרות</t>
+  </si>
+  <si>
+    <t>לשנות את הקישור של הפרופיל ששלח הצעה לקישור לאתר עם הדומיין האמיתי</t>
   </si>
 </sst>
 </file>
@@ -617,10 +623,13 @@
       <c r="B12" t="s">
         <v>16</v>
       </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -650,47 +659,50 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="b">
         <v>0</v>
       </c>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BDD47F-4CF5-4BE4-8980-CE1AD5F688C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77DCB23-BC15-451E-AE44-5714A3FB3A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -102,6 +102,15 @@
   </si>
   <si>
     <t>לשנות את הקישור של הפרופיל ששלח הצעה לקישור לאתר עם הדומיין האמיתי</t>
+  </si>
+  <si>
+    <t>כפתור תרומות</t>
+  </si>
+  <si>
+    <t>להרחיב את הרווח בין השורות בcontent card בlatex</t>
+  </si>
+  <si>
+    <t>שאנשים יוכלו להציע פתרון משלהם לשאלות ואנשים אחרים ידרגו אותו</t>
   </si>
 </sst>
 </file>
@@ -671,15 +680,24 @@
       <c r="A18" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77DCB23-BC15-451E-AE44-5714A3FB3A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67457597-2089-4063-B33C-DB54176B753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>שאנשים יוכלו להציע פתרון משלהם לשאלות ואנשים אחרים ידרגו אותו</t>
+  </si>
+  <si>
+    <t>בשאלות מבחן שיהיה אפשר לבחור אם זו שאלה רבת ברירה או שאלה פתוחה ולפי זה יהיו הסקשנים. בשאלות תרגול שיהיה ניתן לבחור אם זו שאלה רבת ברירה, שאלה פתוחה, flashcard או משהו אחר ואז הסקשנים יהיו בהתאם.</t>
+  </si>
+  <si>
+    <t>שהשאלות בpractice יהיו גם שאלות מבחן ושאלות תרגול מהתוכן שהמשתמש הוסיף</t>
   </si>
 </sst>
 </file>
@@ -704,10 +710,16 @@
       <c r="A21" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67457597-2089-4063-B33C-DB54176B753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EA668F-0539-474E-8C84-F45EAE1201CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -117,6 +117,27 @@
   </si>
   <si>
     <t>שהשאלות בpractice יהיו גם שאלות מבחן ושאלות תרגול מהתוכן שהמשתמש הוסיף</t>
+  </si>
+  <si>
+    <t>שיהיה אפשר לסמן באימון רק שאלות שיש להם פתרון - רשמי או קהילה</t>
+  </si>
+  <si>
+    <t>שבשאלות רבות ברירה תופיע השאלה ומתחתיה 4 האפשרויות וכפתור show solution בדף התוכן. בדף האימון שיופיע הפתרון רק אחרי בחירה של אפשרות</t>
+  </si>
+  <si>
+    <t>שבshow solution אם אין פתרון זמין לא יהיה כתוב אין פתרון זמין לשאלה זו. הוסף פתרון משלך למטה. אלא יהיה כתוב באנגלית</t>
+  </si>
+  <si>
+    <t>הbar של הprogress לא מתעדכן לפי השאלות שפתרתי. שיתעדכן רק לפי השאלות שפתרתי נכון.</t>
+  </si>
+  <si>
+    <t>אם נמחקה שאלה אז גם הcontributions של משתמשים לשאלה צריכים להמחק</t>
+  </si>
+  <si>
+    <t>לדברים שהם לא שאלות אין סיבה שיהיה כפתור reveal solution וcommunity solutions בדף תוכן ובדף תרגול. בדף תרגול צריך להיות כפתור להראות כל סקשן. למשל באלגוריתם במצב אימון צריך להיות כפתור שמראה את הקשן של האלגוריתם וכפתור שמראה את הסקשן של ההוכחה</t>
+  </si>
+  <si>
+    <t>שהצבע בפס העליון שבכרטיס של תוכן יהיה לפי הרמת קושי של התוכן ולא לפי הtype</t>
   </si>
 </sst>
 </file>
@@ -523,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -541,7 +562,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -617,7 +638,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -700,7 +721,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -708,7 +729,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
@@ -726,14 +747,95 @@
       <c r="A23" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -742,5 +844,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EA668F-0539-474E-8C84-F45EAE1201CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C028DF7-B0CB-48EC-BCA6-1C1964FE1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -107,9 +107,6 @@
     <t>כפתור תרומות</t>
   </si>
   <si>
-    <t>להרחיב את הרווח בין השורות בcontent card בlatex</t>
-  </si>
-  <si>
     <t>שאנשים יוכלו להציע פתרון משלהם לשאלות ואנשים אחרים ידרגו אותו</t>
   </si>
   <si>
@@ -138,6 +135,21 @@
   </si>
   <si>
     <t>שהצבע בפס העליון שבכרטיס של תוכן יהיה לפי הרמת קושי של התוכן ולא לפי הtype</t>
+  </si>
+  <si>
+    <t>שיהיה בסרגל כלים בתיבה של הוספת תוכן גם bold, italics, underscore, וכל אלה</t>
+  </si>
+  <si>
+    <t>להרחיב את הרווח בין השורות בcontent card בlatex לברירת מחדל</t>
+  </si>
+  <si>
+    <t>שיהיה בסרגל כלים בתיבה של הוספת תוכן כפתור מעבר לrtl או ltr</t>
+  </si>
+  <si>
+    <t>שיניתי את הרמת קושי של תוכן והיא לא השתנתה אחרי שלחצתי שמור</t>
+  </si>
+  <si>
+    <t>שהשאלות באימון יהיו מהסוגים: שאלות מבחן, שאלות תרגול, שאלות מעורבבות, חזרה כללית על החומר</t>
   </si>
 </sst>
 </file>
@@ -716,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
@@ -724,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
@@ -732,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
@@ -740,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -748,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -756,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -764,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
@@ -772,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
@@ -780,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -788,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -796,45 +808,57 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="b">
         <v>0</v>
       </c>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C028DF7-B0CB-48EC-BCA6-1C1964FE1B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F69507-89D4-4A28-9C57-9DF58E20D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -821,7 +821,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
         <v>36</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F69507-89D4-4A28-9C57-9DF58E20D664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63751F1-0068-4DBB-8651-FBD06DB42C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>שהשאלות באימון יהיו מהסוגים: שאלות מבחן, שאלות תרגול, שאלות מעורבבות, חזרה כללית על החומר</t>
+  </si>
+  <si>
+    <t>לבדוק איך fork עובד</t>
   </si>
 </sst>
 </file>
@@ -847,6 +850,9 @@
       <c r="A34" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="b">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63751F1-0068-4DBB-8651-FBD06DB42C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473AF728-86A7-4911-8ABF-C1FD1DE53E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -768,7 +768,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -840,7 +840,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473AF728-86A7-4911-8ABF-C1FD1DE53E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666703A3-E09D-48AC-A96A-F067EF736E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -848,7 +848,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
         <v>38</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666703A3-E09D-48AC-A96A-F067EF736E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472279D8-3734-4E7D-857D-21E68FB98010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -712,7 +712,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="s">
         <v>25</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472279D8-3734-4E7D-857D-21E68FB98010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B614FF-6CF6-4F6E-9313-7ECD5AB4B8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B614FF-6CF6-4F6E-9313-7ECD5AB4B8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A68F14-B04A-4DEB-A6CD-6593F7A0C62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>לבדוק איך fork עובד</t>
+  </si>
+  <si>
+    <t>השם של הגרסה שאני רשומה אליה ונמצאת בעמוד בית הוא השם המקורי שנתתי לה ולא הפורמט של מוסד*שנה*סמסטר</t>
+  </si>
+  <si>
+    <t>כפתור סינון העמוד של הגרסה צריך להיות עם רקע</t>
+  </si>
+  <si>
+    <t>search courses בשורת חיפוש</t>
   </si>
 </sst>
 </file>
@@ -858,15 +867,24 @@
       <c r="A35" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A68F14-B04A-4DEB-A6CD-6593F7A0C62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7DF9B3-835E-4195-8CA3-D91B6087545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -161,7 +161,19 @@
     <t>כפתור סינון העמוד של הגרסה צריך להיות עם רקע</t>
   </si>
   <si>
-    <t>search courses בשורת חיפוש</t>
+    <t>כפתור info בadd content שמסביר שאפשר להעלות את התמונה לצאט ולתת לו לכתוב latex</t>
+  </si>
+  <si>
+    <t>בadd constent נפתח אוטמטית על התבנית של הוכחה למרות שמחקתי אותה והדבר הראשון זה משהו אחר</t>
+  </si>
+  <si>
+    <t>שמספר הitmes למעלה בגרסה יהיה של כל התוכן ולא ישתנה לפי הקטגוריה שאנחנו בה</t>
+  </si>
+  <si>
+    <t>אופציה לשמור סקשנים כתבנית לדברים הבאים</t>
+  </si>
+  <si>
+    <t>שיהיה אפשר בשורת חיפוש גם לחפש תוכן של קורסים ושם מוסד</t>
   </si>
 </sst>
 </file>
@@ -568,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -884,7 +896,74 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7DF9B3-835E-4195-8CA3-D91B6087545E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD721F8-0062-4AAB-814D-40F386DF6B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -134,9 +134,6 @@
     <t>לדברים שהם לא שאלות אין סיבה שיהיה כפתור reveal solution וcommunity solutions בדף תוכן ובדף תרגול. בדף תרגול צריך להיות כפתור להראות כל סקשן. למשל באלגוריתם במצב אימון צריך להיות כפתור שמראה את הקשן של האלגוריתם וכפתור שמראה את הסקשן של ההוכחה</t>
   </si>
   <si>
-    <t>שהצבע בפס העליון שבכרטיס של תוכן יהיה לפי הרמת קושי של התוכן ולא לפי הtype</t>
-  </si>
-  <si>
     <t>שיהיה בסרגל כלים בתיבה של הוספת תוכן גם bold, italics, underscore, וכל אלה</t>
   </si>
   <si>
@@ -164,16 +161,25 @@
     <t>כפתור info בadd content שמסביר שאפשר להעלות את התמונה לצאט ולתת לו לכתוב latex</t>
   </si>
   <si>
-    <t>בadd constent נפתח אוטמטית על התבנית של הוכחה למרות שמחקתי אותה והדבר הראשון זה משהו אחר</t>
-  </si>
-  <si>
     <t>שמספר הitmes למעלה בגרסה יהיה של כל התוכן ולא ישתנה לפי הקטגוריה שאנחנו בה</t>
   </si>
   <si>
-    <t>אופציה לשמור סקשנים כתבנית לדברים הבאים</t>
-  </si>
-  <si>
     <t>שיהיה אפשר בשורת חיפוש גם לחפש תוכן של קורסים ושם מוסד</t>
+  </si>
+  <si>
+    <t>הגרסה בדף בית צריכה להיות בפורמט הזה HUJI · 2026 · Semester A כרגע לא כתוב את המילה Semester</t>
+  </si>
+  <si>
+    <t>שבדף של הגרסה תהיה אופציה לחפש תוכן</t>
+  </si>
+  <si>
+    <t>שהצבע בפס העליון שבכרטיס של תוכן יהיה לפי הtopic ולא לפי הtype</t>
+  </si>
+  <si>
+    <t>add content נפתח אוטמטית על התבנית של הוכחה למרות שמחקתי אותה מהtypes והדבר הראשון זה משהו אחר</t>
+  </si>
+  <si>
+    <t>כשאני עורכת סקשנים בעריכה של כרטיס תוכן שיהיה אפשר לשמור את העריכה הזו כברירת מחדל לtype הזה בדף הזה של הגרסה</t>
   </si>
 </sst>
 </file>
@@ -749,10 +755,10 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
@@ -829,10 +835,10 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
@@ -840,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
@@ -848,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -856,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
@@ -864,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
@@ -872,31 +878,31 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
@@ -904,23 +910,23 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -928,17 +934,23 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD721F8-0062-4AAB-814D-40F386DF6B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C4B9EB-AC2B-4BDD-8F1E-BB7F7C92A1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>כשאני עורכת סקשנים בעריכה של כרטיס תוכן שיהיה אפשר לשמור את העריכה הזו כברירת מחדל לtype הזה בדף הזה של הגרסה</t>
+  </si>
+  <si>
+    <t>בשאלות שהן flash cards לא צריך שיהיה community solutions</t>
   </si>
 </sst>
 </file>
@@ -957,6 +960,9 @@
       <c r="A44" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="b">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C4B9EB-AC2B-4BDD-8F1E-BB7F7C92A1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5537CD4A-429E-4F5E-963A-0703E6871F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -183,6 +183,27 @@
   </si>
   <si>
     <t>בשאלות שהן flash cards לא צריך שיהיה community solutions</t>
+  </si>
+  <si>
+    <t>generate questions</t>
+  </si>
+  <si>
+    <t>אני רוצה שיהיה משתמש admin שאוסיף ישירות בsupabase שיכול לערוך את כל התוכן באתר</t>
+  </si>
+  <si>
+    <t>אופציה להעלות תמונות בכרטיסי תוכן - צריך להיות הכי יעיל שאפשר ולכווץ את התמונות כמה שיותר. תן לי תוכנית קודם. שימוש בsupabase storage.</t>
+  </si>
+  <si>
+    <t>שדרך המשתמש Admin יהיה אפשר לשלוח הודעות למשתמשי האתר שיקפצו להם בלוח הודעות</t>
+  </si>
+  <si>
+    <t>תגובות בעמוד של הגרסה של הקורס</t>
+  </si>
+  <si>
+    <t>דירוג גרסה</t>
+  </si>
+  <si>
+    <t>שכפתור דיווח על טעות ישלח מייל לא רק לכותב הגרסה אלא גם אליי</t>
   </si>
 </sst>
 </file>
@@ -589,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -958,7 +979,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
@@ -968,20 +989,56 @@
       <c r="A45" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5537CD4A-429E-4F5E-963A-0703E6871F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E700FA6-65D9-468A-8D60-A493990022CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>שכפתור דיווח על טעות ישלח מייל לא רק לכותב הגרסה אלא גם אליי</t>
+  </si>
+  <si>
+    <t>כשעושים fork בלי שמחוברים למשתמש שיהיה כתוב שצריך להתחבר כדי לעשות fork ולא unauthorized</t>
   </si>
 </sst>
 </file>
@@ -610,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -995,7 +998,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -1039,6 +1042,14 @@
       </c>
       <c r="B51" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E700FA6-65D9-468A-8D60-A493990022CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A5EE5-A49B-4CDA-A8A8-F0DFA2C66947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>כשעושים fork בלי שמחוברים למשתמש שיהיה כתוב שצריך להתחבר כדי לעשות fork ולא unauthorized</t>
+  </si>
+  <si>
+    <t>בcontributions בפרופיל שיהיה קישור לcontribution. כרגע יש לגרסאות אבל לא לפתרונות</t>
   </si>
 </sst>
 </file>
@@ -613,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1052,6 +1055,29 @@
         <v>56</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A5EE5-A49B-4CDA-A8A8-F0DFA2C66947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F995A4-B7D5-4E47-9AD1-B0F80BD06053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>בcontributions בפרופיל שיהיה קישור לcontribution. כרגע יש לגרסאות אבל לא לפתרונות</t>
+  </si>
+  <si>
+    <t>שיהיה אפשר לראות את הcommunity solutions רק כשעוברים לtab של הפתרון</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
         <v>52</v>
@@ -1041,7 +1044,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>55</v>
@@ -1049,7 +1052,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>56</v>
@@ -1057,7 +1060,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
@@ -1065,7 +1068,10 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F995A4-B7D5-4E47-9AD1-B0F80BD06053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7807BE9-0B98-443B-8114-3A7012BD80DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>שיהיה אפשר לראות את הcommunity solutions רק כשעוברים לtab של הפתרון</t>
+  </si>
+  <si>
+    <t>שלחיצה על כל הכפתור של הגרסה יכניס לגרסה ולא רק על הכותרת שלה</t>
   </si>
 </sst>
 </file>
@@ -1078,6 +1081,9 @@
       <c r="A55" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B55" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="b">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7807BE9-0B98-443B-8114-3A7012BD80DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1811ED4-8AE5-4EB4-BDAE-8AF48ADF62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>שלחיצה על כל הכפתור של הגרסה יכניס לגרסה ולא רק על הכותרת שלה</t>
+  </si>
+  <si>
+    <t>תרגול לפי סוגי שאלות - flashcards, רבות ברירה, פתוחות</t>
+  </si>
+  <si>
+    <t>העלאת קבצי pdf - דרייב</t>
   </si>
 </sst>
 </file>
@@ -622,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1039,7 +1045,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -1088,6 +1094,17 @@
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1811ED4-8AE5-4EB4-BDAE-8AF48ADF62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B3C351-649A-44F7-A485-D090FE7DCB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>העלאת קבצי pdf - דרייב</t>
+  </si>
+  <si>
+    <t>העלאת תמונות כתוכן</t>
   </si>
 </sst>
 </file>
@@ -628,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1101,10 +1104,28 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B3C351-649A-44F7-A485-D090FE7DCB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF61DA4-9C03-4029-A066-6B0E3CE7F236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>העלאת תמונות כתוכן</t>
+  </si>
+  <si>
+    <t>practice בסדר רנדומלי</t>
+  </si>
+  <si>
+    <t>שיהיה אפשר לעשות reorder גם לtopics</t>
+  </si>
+  <si>
+    <t>לחיצה פעמיים על content type בעריכה שלהם כדי לשנות לו את השם</t>
   </si>
 </sst>
 </file>
@@ -631,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1122,9 +1131,33 @@
       <c r="A59" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B59" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF61DA4-9C03-4029-A066-6B0E3CE7F236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28AC7D5-49CA-4151-95C0-81AA211EBC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -218,9 +218,6 @@
     <t>שלחיצה על כל הכפתור של הגרסה יכניס לגרסה ולא רק על הכותרת שלה</t>
   </si>
   <si>
-    <t>תרגול לפי סוגי שאלות - flashcards, רבות ברירה, פתוחות</t>
-  </si>
-  <si>
     <t>העלאת קבצי pdf - דרייב</t>
   </si>
   <si>
@@ -234,6 +231,12 @@
   </si>
   <si>
     <t>לחיצה פעמיים על content type בעריכה שלהם כדי לשנות לו את השם</t>
+  </si>
+  <si>
+    <t>פרטים נוספים בהגדרה של גרסה - שם מרצה, מספר קורס</t>
+  </si>
+  <si>
+    <t>תרגול לפי סוגי שאלות - flashcards, רבות ברירה, פתוחות ולפי topics</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
@@ -1116,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
@@ -1124,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
@@ -1132,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
@@ -1140,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
@@ -1148,12 +1151,15 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28AC7D5-49CA-4151-95C0-81AA211EBC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6D358A-8194-4E11-B175-F1AE0279EDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -237,6 +237,45 @@
   </si>
   <si>
     <t>תרגול לפי סוגי שאלות - flashcards, רבות ברירה, פתוחות ולפי topics</t>
+  </si>
+  <si>
+    <t>בtopics בpractice צריך להופיע גם תכנים שאין להם נושא. להוסיף כפתור no topic</t>
+  </si>
+  <si>
+    <t>למחוק מהכרטיסי תוכן את האופציה להוסיף רמת קושי</t>
+  </si>
+  <si>
+    <t>שעל שאלות שסומנו בעבר בדרגות קושי יהיה סימון בסשנים הבאים של הדרגות קושי שהמשתמש סימן. ושעל שאלות again שמופיעות סוף הסשן שוב יהיה סימון שהן מופיעות שוב</t>
+  </si>
+  <si>
+    <t>בmy progress שיהיה אפשר לבחור יותר מרמת קושי אחת</t>
+  </si>
+  <si>
+    <t>שsession length יתעדכן גם לפי מה שבחרתי בmy progress ושהמספרים בmy progress יתעדכנו בהתאם לבחירות למעלה</t>
+  </si>
+  <si>
+    <t>שהprogress bar יתקדם לפי תוכן שהמשתמש ענה עליו ok או easy</t>
+  </si>
+  <si>
+    <t>שעל שאלות מבחן יהיה אפשר לענות solved או not solved. וגם לפי זה יהיה אפשר לעשות סינון. הprogress bar יתקדם גם לפי solved questions.</t>
+  </si>
+  <si>
+    <t>שsolved וnot solved יהיה רלוונטי רק לשאלות מבחן. שהסקשן של הסינון לפי זה יפתח רק אם בוחרים בcontent של שאלות מבחן</t>
+  </si>
+  <si>
+    <t>שסימון של only questions with solutions גם יעדכן את המספרים</t>
+  </si>
+  <si>
+    <t>כפתור סימן שאלה שהמשתמש admin יכול לערוך את התוכן שם וכל המשתמשים יכולים לראות. שיהיה ליד הפעמון.</t>
+  </si>
+  <si>
+    <t>שבעריכה של שאלות מבחן אי אפשר יהיה למחוק או לערוך את הסקשנים - שיהיה רק content וsolution</t>
+  </si>
+  <si>
+    <t>שכפתור חזור מהתרגול יוביל חזרה לדף של הגרסה ולא לעמוד בית</t>
+  </si>
+  <si>
+    <t>שהברירת מחדל של קטגוריות בגרסה יהיה רק Exam Question וExercise</t>
   </si>
 </sst>
 </file>
@@ -643,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1108,7 +1147,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>66</v>
@@ -1132,7 +1171,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -1164,6 +1203,120 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6D358A-8194-4E11-B175-F1AE0279EDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAC2583-06DD-4074-9ECD-A32D6C653617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>שהברירת מחדל של קטגוריות בגרסה יהיה רק Exam Question וExercise</t>
+  </si>
+  <si>
+    <t>בעריכה של כרטיס תוכן שיהיה אפשר לערוך גם את הcontent type</t>
   </si>
 </sst>
 </file>
@@ -1309,6 +1312,9 @@
       <c r="A76" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B76" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="b">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAC2583-06DD-4074-9ECD-A32D6C653617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F283A07E-8E99-41A3-B7BF-93A56D6345E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -230,9 +230,6 @@
     <t>שיהיה אפשר לעשות reorder גם לtopics</t>
   </si>
   <si>
-    <t>לחיצה פעמיים על content type בעריכה שלהם כדי לשנות לו את השם</t>
-  </si>
-  <si>
     <t>פרטים נוספים בהגדרה של גרסה - שם מרצה, מספר קורס</t>
   </si>
   <si>
@@ -269,16 +266,22 @@
     <t>כפתור סימן שאלה שהמשתמש admin יכול לערוך את התוכן שם וכל המשתמשים יכולים לראות. שיהיה ליד הפעמון.</t>
   </si>
   <si>
-    <t>שבעריכה של שאלות מבחן אי אפשר יהיה למחוק או לערוך את הסקשנים - שיהיה רק content וsolution</t>
-  </si>
-  <si>
     <t>שכפתור חזור מהתרגול יוביל חזרה לדף של הגרסה ולא לעמוד בית</t>
   </si>
   <si>
-    <t>שהברירת מחדל של קטגוריות בגרסה יהיה רק Exam Question וExercise</t>
-  </si>
-  <si>
     <t>בעריכה של כרטיס תוכן שיהיה אפשר לערוך גם את הcontent type</t>
+  </si>
+  <si>
+    <t>כרגע בעמוד בית הכפתורים שמובילים לגרסאות מופיעים עם שם הקורס באפור למעלה ואז בכחול כהה את הפרטים של הגרסה. אני רוצה להפוך ביניהם. שהפרטיםי של הגרסה יהיו באפור למעלה ומה שבולט יהיה שם הקורס.</t>
+  </si>
+  <si>
+    <t>שבעריכה של שאלות, כל סוג שאלה, אי אפשר יהיה למחוק או לערוך את הסקשנים</t>
+  </si>
+  <si>
+    <t>שהברירת מחדל של קטגוריות כשפותחים גרסה חדשה יהיה רק Exam Question וExercise</t>
+  </si>
+  <si>
+    <t>לחיצה פעמיים על topic בעריכה שלהם כדי לשנות לו את השם כמו שיש בעריכה של content types</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
@@ -1182,7 +1185,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -1190,10 +1193,10 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
@@ -1201,23 +1204,23 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.45">
@@ -1225,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.45">
@@ -1233,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
@@ -1241,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
@@ -1249,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
@@ -1257,7 +1260,7 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.45">
@@ -1265,15 +1268,15 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
@@ -1281,23 +1284,23 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.45">
@@ -1305,20 +1308,23 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F283A07E-8E99-41A3-B7BF-93A56D6345E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9873E04-BAF9-4B05-B971-571E16B79BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -272,9 +272,6 @@
     <t>בעריכה של כרטיס תוכן שיהיה אפשר לערוך גם את הcontent type</t>
   </si>
   <si>
-    <t>כרגע בעמוד בית הכפתורים שמובילים לגרסאות מופיעים עם שם הקורס באפור למעלה ואז בכחול כהה את הפרטים של הגרסה. אני רוצה להפוך ביניהם. שהפרטיםי של הגרסה יהיו באפור למעלה ומה שבולט יהיה שם הקורס.</t>
-  </si>
-  <si>
     <t>שבעריכה של שאלות, כל סוג שאלה, אי אפשר יהיה למחוק או לערוך את הסקשנים</t>
   </si>
   <si>
@@ -282,6 +279,39 @@
   </si>
   <si>
     <t>לחיצה פעמיים על topic בעריכה שלהם כדי לשנות לו את השם כמו שיש בעריכה של content types</t>
+  </si>
+  <si>
+    <t>לחיצה על האיקס כדי למחוק תמונה לא מחקה אותה מהbucket</t>
+  </si>
+  <si>
+    <t>שתמונה בסקשן תיחשב כcontent ויהיה אפשר לעשות submit גם בלי לכתוב דברים</t>
+  </si>
+  <si>
+    <t>אם יש יותר מתמונה 1 - שיופיעו אחת מתחת לשניה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בpractice שאלות עם תמונה כפתרון לא מופיעות בפילטר כshow questions with solutions </t>
+  </si>
+  <si>
+    <t>בsolution בpractice לא רואים יותר מאת התמונה הראשונה</t>
+  </si>
+  <si>
+    <t>כרגע בעמוד בית הכפתורים שמובילים לגרסאות מופיעים עם שם הקורס באפור למעלה ואז בכחול כהה את הפרטים של הגרסה. אני רוצה להפוך ביניהם. שהפרטים של הגרסה יהיו באפור למעלה ומה שבולט יהיה שם הקורס.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שכל גרסה שמעלים תהיה קודם כdraft ואז כשלוחצים publish זה מחכה לאישור מנהל - שולח מייל למשתמש admin שיאשר את התוכן ורק אז זה עולה כpublic. </t>
+  </si>
+  <si>
+    <t>כשמשמש מוסיף קורס זה שולח מייל לadmin</t>
+  </si>
+  <si>
+    <t>שבשאלות רבות ברירה יהיה אפשר לבחור יותר מתשובה אחת נכונה ושהוספת סקשנים אוטומטית תוסיף אופציות לcorrect answer והכותרת שלהם תהיה אוטומטית Option x כאשר x הוא האות הבאה בסדרה</t>
+  </si>
+  <si>
+    <t>שרק המשתמש admin יוכל למחוק קורסים</t>
+  </si>
+  <si>
+    <t>תוסיף לsession length בpractice את האורך 5</t>
   </si>
 </sst>
 </file>
@@ -688,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1196,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
@@ -1292,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
@@ -1308,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
@@ -1324,11 +1354,101 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B78" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B79" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B83" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B86" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9873E04-BAF9-4B05-B971-571E16B79BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6347F536-8BCC-4B42-BB51-B16AADE2B0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -305,13 +305,13 @@
     <t>כשמשמש מוסיף קורס זה שולח מייל לadmin</t>
   </si>
   <si>
-    <t>שבשאלות רבות ברירה יהיה אפשר לבחור יותר מתשובה אחת נכונה ושהוספת סקשנים אוטומטית תוסיף אופציות לcorrect answer והכותרת שלהם תהיה אוטומטית Option x כאשר x הוא האות הבאה בסדרה</t>
-  </si>
-  <si>
     <t>שרק המשתמש admin יוכל למחוק קורסים</t>
   </si>
   <si>
     <t>תוסיף לsession length בpractice את האורך 5</t>
+  </si>
+  <si>
+    <t>שבשאלות רבות ברירה יהיה אפשר לבחור יותר מתשובה אחת נכונה ושבעריכה הוספת סקשנים אוטומטית תוסיף אופציות לcorrect answer והכותרת שלהם תהיה אוטומטית Option x כאשר x הוא האות הבאה בסדרה</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.45">

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6347F536-8BCC-4B42-BB51-B16AADE2B0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7DD44B-7BDB-4458-9C3A-B5AB678CE448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -312,6 +312,15 @@
   </si>
   <si>
     <t>שבשאלות רבות ברירה יהיה אפשר לבחור יותר מתשובה אחת נכונה ושבעריכה הוספת סקשנים אוטומטית תוסיף אופציות לcorrect answer והכותרת שלהם תהיה אוטומטית Option x כאשר x הוא האות הבאה בסדרה</t>
+  </si>
+  <si>
+    <t>dark mode לאתר</t>
+  </si>
+  <si>
+    <t>שהמשתמש admin יוכל לראות בפרופיל של כל אחד את המייל שלו</t>
+  </si>
+  <si>
+    <t>כאשר הadmin מוחק תוכן מסויים שהמשתמש שהעלה אותו יקבל מייל שזה נמחק בידי הadmin</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1424,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>91</v>
@@ -1441,15 +1450,24 @@
       <c r="A88" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B88" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B89" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7DD44B-7BDB-4458-9C3A-B5AB678CE448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32290EAB-EBE3-45A6-8D0E-971F3D049D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -197,9 +197,6 @@
     <t>שדרך המשתמש Admin יהיה אפשר לשלוח הודעות למשתמשי האתר שיקפצו להם בלוח הודעות</t>
   </si>
   <si>
-    <t>תגובות בעמוד של הגרסה של הקורס</t>
-  </si>
-  <si>
     <t>דירוג גרסה</t>
   </si>
   <si>
@@ -302,12 +299,6 @@
     <t xml:space="preserve">שכל גרסה שמעלים תהיה קודם כdraft ואז כשלוחצים publish זה מחכה לאישור מנהל - שולח מייל למשתמש admin שיאשר את התוכן ורק אז זה עולה כpublic. </t>
   </si>
   <si>
-    <t>כשמשמש מוסיף קורס זה שולח מייל לadmin</t>
-  </si>
-  <si>
-    <t>שרק המשתמש admin יוכל למחוק קורסים</t>
-  </si>
-  <si>
     <t>תוסיף לsession length בpractice את האורך 5</t>
   </si>
   <si>
@@ -321,6 +312,12 @@
   </si>
   <si>
     <t>כאשר הadmin מוחק תוכן מסויים שהמשתמש שהעלה אותו יקבל מייל שזה נמחק בידי הadmin</t>
+  </si>
+  <si>
+    <t>שרק המשתמש admin יוכל למחוק ולהוסיף קורסים</t>
+  </si>
+  <si>
+    <t>אם אין קורס שמשתמש רוצה בעמוד של כל הקורסים יש טופס שהוא שולח בקשה וזה מגייע למייל של הadmin כדי שהוא יוסיף את הקורס (כשהadmin מוסיף את הקורס הוא שולח במייל למשתמש שהקורס התווסף ושהוא יכול להעלות את הגרסה הראשונה)</t>
   </si>
 </sst>
 </file>
@@ -727,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -753,7 +750,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -813,7 +810,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1072,7 +1069,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -1120,7 +1117,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
@@ -1136,7 +1133,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
         <v>53</v>
@@ -1176,7 +1173,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
@@ -1184,10 +1181,10 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
@@ -1195,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
@@ -1208,7 +1205,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
@@ -1227,23 +1224,23 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">
@@ -1275,7 +1272,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
@@ -1283,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
@@ -1291,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
@@ -1312,7 +1309,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
@@ -1320,10 +1317,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
@@ -1331,23 +1328,23 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
@@ -1355,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
@@ -1363,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.45">
@@ -1387,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.45">
@@ -1395,15 +1392,15 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.45">
@@ -1411,12 +1408,12 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>88</v>
@@ -1427,15 +1424,15 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
@@ -1451,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.45">
@@ -1459,15 +1456,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A90" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B90" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32290EAB-EBE3-45A6-8D0E-971F3D049D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8681E42E-64E1-4F35-8867-367AF66CFECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -317,7 +317,7 @@
     <t>שרק המשתמש admin יוכל למחוק ולהוסיף קורסים</t>
   </si>
   <si>
-    <t>אם אין קורס שמשתמש רוצה בעמוד של כל הקורסים יש טופס שהוא שולח בקשה וזה מגייע למייל של הadmin כדי שהוא יוסיף את הקורס (כשהadmin מוסיף את הקורס הוא שולח במייל למשתמש שהקורס התווסף ושהוא יכול להעלות את הגרסה הראשונה)</t>
+    <t>אם אין קורס שמשתמש רוצה בעמוד של כל הקורסים שיהיה טופס שבו הוא יכול לשלוח בקשה לקורס וזה יגיע למייל של הadmin כדי שהוא יוסיף את הקורס (כשהadmin מוסיף את הקורס הוא שולח במייל למשתמש שהקורס התווסף ושהוא יכול להעלות את הגרסה הראשונה)</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>63</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8681E42E-64E1-4F35-8867-367AF66CFECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BA8EA6-DEA9-4F6A-8AB7-3C6861D0357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>אם אין קורס שמשתמש רוצה בעמוד של כל הקורסים שיהיה טופס שבו הוא יכול לשלוח בקשה לקורס וזה יגיע למייל של הadmin כדי שהוא יוסיף את הקורס (כשהadmin מוסיף את הקורס הוא שולח במייל למשתמש שהקורס התווסף ושהוא יכול להעלות את הגרסה הראשונה)</t>
+  </si>
+  <si>
+    <t>מיון קורסים לפי דברים שונים - שלחיצה אחת תמיין מלמטה למעלה ושנייה מלמעלה למטה  - ושיהיה חץ שמראה את זה</t>
   </si>
 </sst>
 </file>
@@ -724,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1459,6 +1462,29 @@
         <v>91</v>
       </c>
     </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BA8EA6-DEA9-4F6A-8AB7-3C6861D0357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1F12EF-AFDC-4FAD-B368-B88600690579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -321,6 +321,15 @@
   </si>
   <si>
     <t>מיון קורסים לפי דברים שונים - שלחיצה אחת תמיין מלמטה למעלה ושנייה מלמעלה למטה  - ושיהיה חץ שמראה את זה</t>
+  </si>
+  <si>
+    <t>כפתור דיווח על גרסה - מגיע לAdmin</t>
+  </si>
+  <si>
+    <t>כל דבר שהadmin משנה בגרסה - כולל אם הוא מוחק אותה - שישלח מייל למי שיצר אותה על השינוי</t>
+  </si>
+  <si>
+    <t>אופציה להחזיר תשובה מותאמת אישית למשתמש שביקש קורס - למשל, שים לב הקורס כבר קיים</t>
   </si>
 </sst>
 </file>
@@ -1474,15 +1483,24 @@
       <c r="A91" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B91" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B92" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1F12EF-AFDC-4FAD-B368-B88600690579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AA0D2A-B04A-4216-8671-322065C31C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>כרגע בעמוד בית הכפתורים שמובילים לגרסאות מופיעים עם שם הקורס באפור למעלה ואז בכחול כהה את הפרטים של הגרסה. אני רוצה להפוך ביניהם. שהפרטים של הגרסה יהיו באפור למעלה ומה שבולט יהיה שם הקורס.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שכל גרסה שמעלים תהיה קודם כdraft ואז כשלוחצים publish זה מחכה לאישור מנהל - שולח מייל למשתמש admin שיאשר את התוכן ורק אז זה עולה כpublic. </t>
   </si>
   <si>
     <t>תוסיף לsession length בpractice את האורך 5</t>
@@ -736,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1409,18 +1406,18 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.45">
@@ -1428,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
@@ -1436,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
@@ -1444,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
@@ -1468,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.45">
@@ -1489,18 +1486,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A93" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B93" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AA0D2A-B04A-4216-8671-322065C31C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E45D785-C0FC-4AD7-B4DD-7742B6849262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
         <v>89</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B90" t="s">
         <v>94</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E45D785-C0FC-4AD7-B4DD-7742B6849262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3770FE-37CC-45A0-A835-241E98752306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
         <v>93</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3770FE-37CC-45A0-A835-241E98752306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A03898E-0312-4FB1-B9A8-68941C1F0623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -156,9 +156,6 @@
   </si>
   <si>
     <t>כפתור סינון העמוד של הגרסה צריך להיות עם רקע</t>
-  </si>
-  <si>
-    <t>כפתור info בadd content שמסביר שאפשר להעלות את התמונה לצאט ולתת לו לכתוב latex</t>
   </si>
   <si>
     <t>שמספר הitmes למעלה בגרסה יהיה של כל התוכן ולא ישתנה לפי הקטגוריה שאנחנו בה</t>
@@ -733,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -985,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
@@ -1049,15 +1046,15 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1065,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
@@ -1073,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -1081,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
@@ -1097,12 +1094,12 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>48</v>
@@ -1110,7 +1107,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
@@ -1174,7 +1171,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
@@ -1182,10 +1179,10 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
@@ -1193,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
@@ -1225,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
@@ -1233,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
@@ -1241,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
@@ -1273,7 +1270,7 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.45">
@@ -1281,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
@@ -1289,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
@@ -1318,10 +1315,10 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
@@ -1329,23 +1326,23 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.45">
@@ -1353,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
@@ -1361,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
@@ -1385,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.45">
@@ -1393,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.45">
@@ -1401,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.45">
@@ -1409,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.45">
@@ -1417,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.45">
@@ -1425,20 +1422,20 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
         <v>88</v>
@@ -1446,7 +1443,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
         <v>89</v>
@@ -1454,10 +1451,10 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.45">
@@ -1470,7 +1467,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
         <v>94</v>
@@ -1478,18 +1475,10 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B91" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A92" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B92" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A03898E-0312-4FB1-B9A8-68941C1F0623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14206ED-0F52-44B6-90F2-0D4B06BCEBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>77</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>87</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14206ED-0F52-44B6-90F2-0D4B06BCEBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C5C6F-1A66-4EB0-B64C-1A347D277837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>אופציה להחזיר תשובה מותאמת אישית למשתמש שביקש קורס - למשל, שים לב הקורס כבר קיים</t>
+  </si>
+  <si>
+    <t>במקום כיתוב של הinstitution - בחירה מתוך רשימה. ואז שם מקוצר של המוסד בכותרת של הגרסה ושם מלא בתיאור.</t>
   </si>
 </sst>
 </file>
@@ -730,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1171,7 +1174,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
@@ -1479,6 +1482,29 @@
       </c>
       <c r="B91" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C5C6F-1A66-4EB0-B64C-1A347D277837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44801C37-259E-4513-8374-D964EEA96DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
+    <workbookView xWindow="3247" yWindow="2138" windowWidth="16200" windowHeight="9307" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44801C37-259E-4513-8374-D964EEA96DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B757D9E9-693F-4B29-8B94-36E98EDAB1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3247" yWindow="2138" windowWidth="16200" windowHeight="9307" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>במקום כיתוב של הinstitution - בחירה מתוך רשימה. ואז שם מקוצר של המוסד בכותרת של הגרסה ושם מלא בתיאור.</t>
+  </si>
+  <si>
+    <t>לשלם על railway</t>
+  </si>
+  <si>
+    <t>גרסה מותאמת לmobile</t>
+  </si>
+  <si>
+    <t>google analytics</t>
+  </si>
+  <si>
+    <t>תיצור קובץ מפורט על כל השירותים החיצוניים שהשתמשתי בהם ומה כל אחד עושה ומה צריך בשביל כל אחד</t>
+  </si>
+  <si>
+    <t>תיצור קובץ מפורט שמסביר על הקוד</t>
+  </si>
+  <si>
+    <t>מערכת יותר ברורה לשאלות האמריקאיות</t>
   </si>
 </sst>
 </file>
@@ -733,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1496,15 +1514,48 @@
       <c r="A93" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B93" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B94" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="B95" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B96" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A97" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B97" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A98" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B757D9E9-693F-4B29-8B94-36E98EDAB1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BA528B-8CEC-4891-8916-5D2AC71D3DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3247" yWindow="2138" windowWidth="16200" windowHeight="9307" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>מערכת יותר ברורה לשאלות האמריקאיות</t>
+  </si>
+  <si>
+    <t>פחות nodes ברקע בmobile</t>
+  </si>
+  <si>
+    <t>delete account option</t>
   </si>
 </sst>
 </file>
@@ -751,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1558,6 +1564,22 @@
         <v>102</v>
       </c>
     </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A99" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A100" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BA528B-8CEC-4891-8916-5D2AC71D3DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08F5152-B740-4A42-A887-3065E80D571A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3247" yWindow="2138" windowWidth="16200" windowHeight="9307" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -326,9 +326,6 @@
     <t>אופציה להחזיר תשובה מותאמת אישית למשתמש שביקש קורס - למשל, שים לב הקורס כבר קיים</t>
   </si>
   <si>
-    <t>במקום כיתוב של הinstitution - בחירה מתוך רשימה. ואז שם מקוצר של המוסד בכותרת של הגרסה ושם מלא בתיאור.</t>
-  </si>
-  <si>
     <t>לשלם על railway</t>
   </si>
   <si>
@@ -351,6 +348,24 @@
   </si>
   <si>
     <t>delete account option</t>
+  </si>
+  <si>
+    <t>שינוי שם באתר</t>
+  </si>
+  <si>
+    <t>שאלות רחבות בflashcards יוצאות מגבולות המסך בmobile</t>
+  </si>
+  <si>
+    <t>כשלוחצים בmobile על אחת מהאופציות בflashcards - כלומר קל בסדר או קשה או שוב, יש דילאיי עד שזה עובר לשאלה הבאה</t>
+  </si>
+  <si>
+    <t>במקום כיתוב של הinstitution - בחירה מתוך רשימה. ואז שם מקוצר של המוסד בכותרת של הגרסה ושם מלא בתיאור. והסינון לפי מוסד בדף בית מראה את השם המלא</t>
+  </si>
+  <si>
+    <t>לא צריך את הכפתור למטה של community בmobile</t>
+  </si>
+  <si>
+    <t>סינון הגרסאות לפי מוסד בדף קורס עצמו</t>
   </si>
 </sst>
 </file>
@@ -757,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1513,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.45">
@@ -1521,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.45">
@@ -1529,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.45">
@@ -1537,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.45">
@@ -1545,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.45">
@@ -1553,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.45">
@@ -1561,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.45">
@@ -1569,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.45">
@@ -1577,7 +1592,47 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A101" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B101" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A103" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A104" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B104" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A105" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B105" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08F5152-B740-4A42-A887-3065E80D571A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2887364D-0062-4DB7-9031-4DD06C5C497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
         <v>107</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2887364D-0062-4DB7-9031-4DD06C5C497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C8FF66-84E5-4211-95E8-85C21E7FFF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
         <v>109</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C8FF66-84E5-4211-95E8-85C21E7FFF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D50332D-24D4-4BA1-ACF6-6E5BE94DFD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
         <v>106</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B103" t="s">
         <v>105</v>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" t="s">
         <v>108</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D50332D-24D4-4BA1-ACF6-6E5BE94DFD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828D7557-4510-4252-854F-DB432FF50D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -356,9 +356,6 @@
     <t>שאלות רחבות בflashcards יוצאות מגבולות המסך בmobile</t>
   </si>
   <si>
-    <t>כשלוחצים בmobile על אחת מהאופציות בflashcards - כלומר קל בסדר או קשה או שוב, יש דילאיי עד שזה עובר לשאלה הבאה</t>
-  </si>
-  <si>
     <t>במקום כיתוב של הinstitution - בחירה מתוך רשימה. ואז שם מקוצר של המוסד בכותרת של הגרסה ושם מלא בתיאור. והסינון לפי מוסד בדף בית מראה את השם המלא</t>
   </si>
   <si>
@@ -366,6 +363,29 @@
   </si>
   <si>
     <t>סינון הגרסאות לפי מוסד בדף קורס עצמו</t>
+  </si>
+  <si>
+    <t>עדיין כשלוחצים בmobile על אחת מהאופציות בflashcards - כלומר קל בסדר או קשה או שוב, יש דילאיי עד שזה עובר לשאלה הבאה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">באתר הdeployed אני לא מצליחה להגיש בקשה לקורס. זה כותב Unauthorized
+</t>
+  </si>
+  <si>
+    <t>לבדוק את כל הקישורים בהודעות במייל</t>
+  </si>
+  <si>
+    <t>הסינון לפי subject בעמוד של כל הקורסים צריך להיות כמו הכפתור dropsown שיש בדף בית</t>
+  </si>
+  <si>
+    <t>באתר הdeployed בתור admin אני לא מצליחה ליצור קורס. זה כותב Unauthorized
+ או שזה נתקע ויוצר אבל הכפתור נשאר תקוע</t>
+  </si>
+  <si>
+    <t>לא כי אז ימחק תוכן</t>
+  </si>
+  <si>
+    <t>שהadmin יוכל לחפש משתמשים באתר ולהכנס לפרופיל שלהם</t>
   </si>
 </sst>
 </file>
@@ -409,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -421,6 +441,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1528,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.45">
@@ -1563,7 +1584,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="b">
         <v>0</v>
       </c>
@@ -1571,7 +1592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1600,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="b">
         <v>1</v>
       </c>
@@ -1587,15 +1608,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="b">
         <v>0</v>
       </c>
       <c r="B100" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C100" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="b">
         <v>0</v>
       </c>
@@ -1603,15 +1627,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="b">
         <v>1</v>
       </c>
@@ -1619,20 +1643,65 @@
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="b">
         <v>1</v>
       </c>
       <c r="B104" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="B105" t="s">
-        <v>109</v>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A108" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A110" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A111" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828D7557-4510-4252-854F-DB432FF50D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29206819-EF5F-4022-9076-F76E786AC023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -429,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -441,7 +441,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1663,7 +1662,7 @@
       <c r="A106" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1671,7 +1670,7 @@
       <c r="A107" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1679,7 +1678,7 @@
       <c r="A108" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1687,15 +1686,15 @@
       <c r="A109" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="B110" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
         <v>115</v>
       </c>
     </row>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29206819-EF5F-4022-9076-F76E786AC023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5492F7B5-20D2-4304-B121-674D9CA488AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B108" t="s">
         <v>112</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5492F7B5-20D2-4304-B121-674D9CA488AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20150189-9F73-4B48-9FDE-C1BBD680F3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -1561,7 +1561,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
         <v>97</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
         <v>109</v>

--- a/docs/tasks-lambda.xlsx
+++ b/docs/tasks-lambda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\Lambda\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20150189-9F73-4B48-9FDE-C1BBD680F3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B08060-AA14-41CB-9B36-38CCDF7264A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{64494733-B6F9-48B6-9193-F7C7FF2B1841}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>הוספה של אופציה להוסיף שאלות כלליות (לאו דווקא ממבחן) - רבות ברירה, שאלות פתוחות</t>
   </si>
@@ -386,6 +386,15 @@
   </si>
   <si>
     <t>שהadmin יוכל לחפש משתמשים באתר ולהכנס לפרופיל שלהם</t>
+  </si>
+  <si>
+    <t>שהadmin יוכל למחוק community solution</t>
+  </si>
+  <si>
+    <t>להוסיף קישור בין כרטיסי תוכן. אופציה לסמן מילה ולהוסיף אותה כקישור לכרטיס אחר.</t>
+  </si>
+  <si>
+    <t>להוסיף אופציה לכתוב בצבעים שונים.</t>
   </si>
 </sst>
 </file>
@@ -792,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABCB3E3-AEE1-47E5-A283-0150B72CF279}">
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1702,6 +1711,30 @@
       <c r="A111" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="B111" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A112" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B112" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A113" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="B113" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A114" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
